--- a/outputs/Fuel_(diesel,_parallel_market)_tukey_classification_matrix.xlsx
+++ b/outputs/Fuel_(diesel,_parallel_market)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="142">
   <si>
     <t>2018 Mar</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -1186,76 +1189,76 @@
         <v>126</v>
       </c>
       <c r="X2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z2" t="s">
         <v>126</v>
       </c>
       <c r="AA2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL2" t="s">
         <v>126</v>
       </c>
       <c r="AM2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN2" t="s">
         <v>126</v>
       </c>
       <c r="AO2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV2" t="s">
         <v>126</v>
@@ -1402,13 +1405,13 @@
         <v>126</v>
       </c>
       <c r="CR2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:98">
@@ -1530,7 +1533,7 @@
         <v>126</v>
       </c>
       <c r="AN3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO3" t="s">
         <v>126</v>
@@ -1539,16 +1542,16 @@
         <v>126</v>
       </c>
       <c r="AQ3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU3" t="s">
         <v>126</v>
@@ -1563,25 +1566,25 @@
         <v>126</v>
       </c>
       <c r="AY3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ3" t="s">
         <v>126</v>
       </c>
       <c r="BA3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF3" t="s">
         <v>126</v>
@@ -1590,28 +1593,28 @@
         <v>126</v>
       </c>
       <c r="BH3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI3" t="s">
         <v>126</v>
       </c>
       <c r="BJ3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP3" t="s">
         <v>126</v>
@@ -1635,25 +1638,25 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX3" t="s">
         <v>126</v>
       </c>
       <c r="BY3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ3" t="s">
         <v>126</v>
       </c>
       <c r="CA3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD3" t="s">
         <v>126</v>
@@ -1662,31 +1665,31 @@
         <v>126</v>
       </c>
       <c r="CF3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG3" t="s">
         <v>126</v>
       </c>
       <c r="CH3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI3" t="s">
         <v>126</v>
       </c>
       <c r="CJ3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CK3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL3" t="s">
         <v>126</v>
       </c>
       <c r="CM3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO3" t="s">
         <v>126</v>
@@ -1698,13 +1701,13 @@
         <v>126</v>
       </c>
       <c r="CR3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:98">
@@ -1712,295 +1715,295 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN4" t="s">
         <v>126</v>
       </c>
       <c r="AO4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR4" t="s">
         <v>126</v>
       </c>
       <c r="AS4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV4" t="s">
         <v>126</v>
       </c>
       <c r="BW4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CG4" t="s">
         <v>128</v>
       </c>
-      <c r="CF4" t="s">
-        <v>126</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>127</v>
-      </c>
       <c r="CH4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK4" t="s">
         <v>126</v>
       </c>
       <c r="CL4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CO4" t="s">
         <v>128</v>
       </c>
-      <c r="CO4" t="s">
-        <v>127</v>
-      </c>
       <c r="CP4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CQ4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CR4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="CS4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="CT4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:98">
@@ -2125,157 +2128,157 @@
         <v>126</v>
       </c>
       <c r="AO5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT5" t="s">
         <v>126</v>
       </c>
       <c r="AU5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV5" t="s">
         <v>126</v>
       </c>
       <c r="AW5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY5" t="s">
         <v>126</v>
       </c>
       <c r="AZ5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD5" t="s">
         <v>126</v>
       </c>
       <c r="BE5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL5" t="s">
         <v>126</v>
       </c>
       <c r="BM5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS5" t="s">
         <v>126</v>
       </c>
       <c r="BT5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY5" t="s">
         <v>126</v>
       </c>
       <c r="BZ5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD5" t="s">
         <v>126</v>
       </c>
       <c r="CE5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG5" t="s">
         <v>126</v>
       </c>
       <c r="CH5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI5" t="s">
         <v>126</v>
       </c>
       <c r="CJ5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN5" t="s">
         <v>126</v>
@@ -2290,13 +2293,13 @@
         <v>126</v>
       </c>
       <c r="CR5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:98">
@@ -2433,43 +2436,43 @@
         <v>126</v>
       </c>
       <c r="AS6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT6" t="s">
         <v>126</v>
       </c>
       <c r="AU6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV6" t="s">
         <v>126</v>
       </c>
       <c r="AW6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX6" t="s">
         <v>126</v>
       </c>
       <c r="AY6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD6" t="s">
         <v>126</v>
       </c>
       <c r="BE6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF6" t="s">
         <v>126</v>
@@ -2478,22 +2481,22 @@
         <v>126</v>
       </c>
       <c r="BH6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK6" t="s">
         <v>126</v>
       </c>
       <c r="BL6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN6" t="s">
         <v>126</v>
@@ -2502,52 +2505,52 @@
         <v>126</v>
       </c>
       <c r="BP6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR6" t="s">
         <v>126</v>
       </c>
       <c r="BS6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY6" t="s">
         <v>126</v>
       </c>
       <c r="BZ6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC6" t="s">
         <v>126</v>
       </c>
       <c r="CD6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF6" t="s">
         <v>126</v>
@@ -2586,13 +2589,13 @@
         <v>126</v>
       </c>
       <c r="CR6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:98">
@@ -2774,7 +2777,7 @@
         <v>126</v>
       </c>
       <c r="BH7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI7" t="s">
         <v>126</v>
@@ -2825,10 +2828,10 @@
         <v>126</v>
       </c>
       <c r="BY7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA7" t="s">
         <v>126</v>
@@ -2867,7 +2870,7 @@
         <v>126</v>
       </c>
       <c r="CM7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN7" t="s">
         <v>126</v>
@@ -2882,13 +2885,13 @@
         <v>126</v>
       </c>
       <c r="CR7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -3013,22 +3016,22 @@
         <v>126</v>
       </c>
       <c r="AO8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP8" t="s">
         <v>126</v>
       </c>
       <c r="AQ8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU8" t="s">
         <v>126</v>
@@ -3037,58 +3040,58 @@
         <v>126</v>
       </c>
       <c r="AW8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA8" t="s">
         <v>126</v>
       </c>
       <c r="BB8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF8" t="s">
         <v>126</v>
       </c>
       <c r="BG8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ8" t="s">
         <v>126</v>
       </c>
       <c r="BK8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO8" t="s">
         <v>126</v>
@@ -3109,19 +3112,19 @@
         <v>126</v>
       </c>
       <c r="BU8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW8" t="s">
         <v>126</v>
       </c>
       <c r="BX8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ8" t="s">
         <v>126</v>
@@ -3130,7 +3133,7 @@
         <v>126</v>
       </c>
       <c r="CB8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC8" t="s">
         <v>126</v>
@@ -3142,7 +3145,7 @@
         <v>126</v>
       </c>
       <c r="CF8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG8" t="s">
         <v>126</v>
@@ -3178,13 +3181,13 @@
         <v>126</v>
       </c>
       <c r="CR8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -3192,22 +3195,22 @@
         <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
         <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H9" t="s">
         <v>126</v>
@@ -3216,115 +3219,115 @@
         <v>126</v>
       </c>
       <c r="J9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R9" t="s">
         <v>126</v>
       </c>
       <c r="S9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U9" t="s">
         <v>126</v>
       </c>
       <c r="V9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE9" t="s">
         <v>126</v>
       </c>
       <c r="AF9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ9" t="s">
         <v>126</v>
       </c>
       <c r="AK9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL9" t="s">
         <v>126</v>
       </c>
       <c r="AM9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS9" t="s">
         <v>126</v>
       </c>
       <c r="AT9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU9" t="s">
         <v>126</v>
@@ -3357,28 +3360,28 @@
         <v>126</v>
       </c>
       <c r="BE9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG9" t="s">
         <v>126</v>
       </c>
       <c r="BH9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK9" t="s">
         <v>126</v>
       </c>
       <c r="BL9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM9" t="s">
         <v>126</v>
@@ -3474,13 +3477,13 @@
         <v>126</v>
       </c>
       <c r="CR9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -3488,10 +3491,10 @@
         <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
         <v>126</v>
@@ -3659,7 +3662,7 @@
         <v>126</v>
       </c>
       <c r="BG10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH10" t="s">
         <v>126</v>
@@ -3677,10 +3680,10 @@
         <v>126</v>
       </c>
       <c r="BM10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO10" t="s">
         <v>126</v>
@@ -3710,13 +3713,13 @@
         <v>126</v>
       </c>
       <c r="BX10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY10" t="s">
         <v>126</v>
       </c>
       <c r="BZ10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA10" t="s">
         <v>126</v>
@@ -3770,13 +3773,13 @@
         <v>126</v>
       </c>
       <c r="CR10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -4036,19 +4039,19 @@
         <v>126</v>
       </c>
       <c r="CH11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM11" t="s">
         <v>126</v>
@@ -4066,13 +4069,13 @@
         <v>126</v>
       </c>
       <c r="CR11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -4254,7 +4257,7 @@
         <v>126</v>
       </c>
       <c r="BH12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI12" t="s">
         <v>126</v>
@@ -4263,19 +4266,19 @@
         <v>126</v>
       </c>
       <c r="BK12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP12" t="s">
         <v>126</v>
@@ -4302,10 +4305,10 @@
         <v>126</v>
       </c>
       <c r="BX12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ12" t="s">
         <v>126</v>
@@ -4323,31 +4326,31 @@
         <v>126</v>
       </c>
       <c r="CE12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF12" t="s">
         <v>126</v>
       </c>
       <c r="CG12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CH12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI12" t="s">
         <v>126</v>
       </c>
       <c r="CJ12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK12" t="s">
         <v>126</v>
       </c>
       <c r="CL12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN12" t="s">
         <v>126</v>
@@ -4362,13 +4365,13 @@
         <v>126</v>
       </c>
       <c r="CR12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -4550,28 +4553,28 @@
         <v>126</v>
       </c>
       <c r="BH13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL13" t="s">
         <v>126</v>
       </c>
       <c r="BM13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP13" t="s">
         <v>126</v>
@@ -4580,13 +4583,13 @@
         <v>126</v>
       </c>
       <c r="BR13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS13" t="s">
         <v>126</v>
       </c>
       <c r="BT13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU13" t="s">
         <v>126</v>
@@ -4598,13 +4601,13 @@
         <v>126</v>
       </c>
       <c r="BX13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY13" t="s">
         <v>126</v>
       </c>
       <c r="BZ13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA13" t="s">
         <v>126</v>
@@ -4622,7 +4625,7 @@
         <v>126</v>
       </c>
       <c r="CF13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG13" t="s">
         <v>126</v>
@@ -4631,40 +4634,40 @@
         <v>126</v>
       </c>
       <c r="CI13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL13" t="s">
         <v>126</v>
       </c>
       <c r="CM13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CP13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CQ13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CR13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -4696,28 +4699,28 @@
         <v>126</v>
       </c>
       <c r="J14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P14" t="s">
         <v>126</v>
       </c>
       <c r="Q14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R14" t="s">
         <v>126</v>
@@ -4732,7 +4735,7 @@
         <v>126</v>
       </c>
       <c r="V14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W14" t="s">
         <v>126</v>
@@ -4741,52 +4744,52 @@
         <v>126</v>
       </c>
       <c r="Y14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH14" t="s">
         <v>126</v>
       </c>
       <c r="AI14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM14" t="s">
         <v>126</v>
       </c>
       <c r="AN14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO14" t="s">
         <v>126</v>
@@ -4798,43 +4801,43 @@
         <v>126</v>
       </c>
       <c r="AR14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS14" t="s">
         <v>126</v>
       </c>
       <c r="AT14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV14" t="s">
         <v>126</v>
       </c>
       <c r="AW14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY14" t="s">
         <v>126</v>
       </c>
       <c r="AZ14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE14" t="s">
         <v>126</v>
@@ -4843,70 +4846,70 @@
         <v>126</v>
       </c>
       <c r="BG14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN14" t="s">
         <v>126</v>
       </c>
       <c r="BO14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP14" t="s">
         <v>126</v>
       </c>
       <c r="BQ14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV14" t="s">
         <v>126</v>
       </c>
       <c r="BW14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC14" t="s">
         <v>126</v>
@@ -4918,16 +4921,16 @@
         <v>126</v>
       </c>
       <c r="CF14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ14" t="s">
         <v>126</v>
@@ -4954,13 +4957,13 @@
         <v>126</v>
       </c>
       <c r="CR14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="CS14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -4968,10 +4971,10 @@
         <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
         <v>126</v>
@@ -5151,19 +5154,19 @@
         <v>126</v>
       </c>
       <c r="BK15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL15" t="s">
         <v>126</v>
       </c>
       <c r="BM15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP15" t="s">
         <v>126</v>
@@ -5172,49 +5175,49 @@
         <v>126</v>
       </c>
       <c r="BR15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU15" t="s">
         <v>126</v>
       </c>
       <c r="BV15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD15" t="s">
         <v>126</v>
       </c>
       <c r="CE15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG15" t="s">
         <v>126</v>
@@ -5229,7 +5232,7 @@
         <v>126</v>
       </c>
       <c r="CK15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL15" t="s">
         <v>126</v>
@@ -5238,25 +5241,25 @@
         <v>126</v>
       </c>
       <c r="CN15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO15" t="s">
         <v>126</v>
       </c>
       <c r="CP15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CQ15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CR15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -5348,19 +5351,19 @@
         <v>126</v>
       </c>
       <c r="AD16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s">
         <v>126</v>
       </c>
       <c r="AH16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI16" t="s">
         <v>126</v>
@@ -5396,10 +5399,10 @@
         <v>126</v>
       </c>
       <c r="AT16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV16" t="s">
         <v>126</v>
@@ -5438,37 +5441,37 @@
         <v>126</v>
       </c>
       <c r="BH16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL16" t="s">
         <v>126</v>
       </c>
       <c r="BM16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO16" t="s">
         <v>126</v>
       </c>
       <c r="BP16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ16" t="s">
         <v>126</v>
       </c>
       <c r="BR16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS16" t="s">
         <v>126</v>
@@ -5480,19 +5483,19 @@
         <v>126</v>
       </c>
       <c r="BV16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY16" t="s">
         <v>126</v>
       </c>
       <c r="BZ16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA16" t="s">
         <v>126</v>
@@ -5501,10 +5504,10 @@
         <v>126</v>
       </c>
       <c r="CC16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE16" t="s">
         <v>126</v>
@@ -5519,7 +5522,7 @@
         <v>126</v>
       </c>
       <c r="CI16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ16" t="s">
         <v>126</v>
@@ -5546,13 +5549,13 @@
         <v>126</v>
       </c>
       <c r="CR16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -5626,73 +5629,73 @@
         <v>126</v>
       </c>
       <c r="X17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z17" t="s">
         <v>126</v>
       </c>
       <c r="AA17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB17" t="s">
         <v>126</v>
       </c>
       <c r="AC17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI17" t="s">
         <v>126</v>
       </c>
       <c r="AJ17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM17" t="s">
         <v>126</v>
       </c>
       <c r="AN17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU17" t="s">
         <v>126</v>
@@ -5701,43 +5704,43 @@
         <v>126</v>
       </c>
       <c r="AW17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX17" t="s">
         <v>126</v>
       </c>
       <c r="AY17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ17" t="s">
         <v>126</v>
@@ -5752,88 +5755,88 @@
         <v>126</v>
       </c>
       <c r="BN17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR17" t="s">
         <v>126</v>
       </c>
       <c r="BS17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU17" t="s">
         <v>126</v>
       </c>
       <c r="BV17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX17" t="s">
         <v>126</v>
       </c>
       <c r="BY17" t="s">
+        <v>129</v>
+      </c>
+      <c r="BZ17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CA17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF17" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG17" t="s">
         <v>128</v>
       </c>
-      <c r="BZ17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CA17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CB17" t="s">
+      <c r="CH17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI17" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ17" t="s">
         <v>128</v>
       </c>
-      <c r="CC17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CD17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CE17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CF17" t="s">
+      <c r="CK17" t="s">
         <v>128</v>
       </c>
-      <c r="CG17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CI17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CJ17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK17" t="s">
-        <v>127</v>
-      </c>
       <c r="CL17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN17" t="s">
         <v>126</v>
       </c>
       <c r="CO17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CP17" t="s">
         <v>126</v>
@@ -5842,13 +5845,13 @@
         <v>126</v>
       </c>
       <c r="CR17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CS17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CT17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -5856,7 +5859,7 @@
         <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
         <v>126</v>
@@ -5883,31 +5886,31 @@
         <v>126</v>
       </c>
       <c r="K18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s">
         <v>126</v>
       </c>
       <c r="M18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O18" t="s">
         <v>126</v>
       </c>
       <c r="P18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q18" t="s">
         <v>126</v>
       </c>
       <c r="R18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T18" t="s">
         <v>126</v>
@@ -5916,10 +5919,10 @@
         <v>126</v>
       </c>
       <c r="V18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X18" t="s">
         <v>126</v>
@@ -5934,10 +5937,10 @@
         <v>126</v>
       </c>
       <c r="AB18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD18" t="s">
         <v>126</v>
@@ -5952,43 +5955,43 @@
         <v>126</v>
       </c>
       <c r="AH18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK18" t="s">
         <v>126</v>
       </c>
       <c r="AL18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU18" t="s">
         <v>126</v>
@@ -6000,22 +6003,22 @@
         <v>126</v>
       </c>
       <c r="AX18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB18" t="s">
         <v>126</v>
       </c>
       <c r="BC18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD18" t="s">
         <v>126</v>
@@ -6024,7 +6027,7 @@
         <v>126</v>
       </c>
       <c r="BF18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG18" t="s">
         <v>126</v>
@@ -6033,25 +6036,25 @@
         <v>126</v>
       </c>
       <c r="BI18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM18" t="s">
         <v>126</v>
       </c>
       <c r="BN18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP18" t="s">
         <v>126</v>
@@ -6060,16 +6063,16 @@
         <v>126</v>
       </c>
       <c r="BR18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV18" t="s">
         <v>126</v>
@@ -6081,70 +6084,70 @@
         <v>126</v>
       </c>
       <c r="BY18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF18" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>129</v>
+      </c>
+      <c r="CJ18" t="s">
         <v>128</v>
       </c>
-      <c r="CG18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CI18" t="s">
+      <c r="CK18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CO18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP18" t="s">
         <v>128</v>
       </c>
-      <c r="CJ18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CL18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CN18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP18" t="s">
-        <v>127</v>
-      </c>
       <c r="CQ18" t="s">
         <v>126</v>
       </c>
       <c r="CR18" t="s">
+        <v>134</v>
+      </c>
+      <c r="CS18" t="s">
         <v>133</v>
       </c>
-      <c r="CS18" t="s">
-        <v>132</v>
-      </c>
       <c r="CT18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -6233,10 +6236,10 @@
         <v>126</v>
       </c>
       <c r="AC19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE19" t="s">
         <v>126</v>
@@ -6248,10 +6251,10 @@
         <v>126</v>
       </c>
       <c r="AH19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ19" t="s">
         <v>126</v>
@@ -6260,43 +6263,43 @@
         <v>126</v>
       </c>
       <c r="AL19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO19" t="s">
         <v>126</v>
       </c>
       <c r="AP19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU19" t="s">
         <v>126</v>
       </c>
       <c r="AV19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY19" t="s">
         <v>126</v>
@@ -6305,19 +6308,19 @@
         <v>126</v>
       </c>
       <c r="BA19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB19" t="s">
         <v>126</v>
       </c>
       <c r="BC19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF19" t="s">
         <v>126</v>
@@ -6326,7 +6329,7 @@
         <v>126</v>
       </c>
       <c r="BH19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI19" t="s">
         <v>126</v>
@@ -6338,10 +6341,10 @@
         <v>126</v>
       </c>
       <c r="BL19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN19" t="s">
         <v>126</v>
@@ -6380,7 +6383,7 @@
         <v>126</v>
       </c>
       <c r="BZ19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA19" t="s">
         <v>126</v>
@@ -6434,13 +6437,13 @@
         <v>126</v>
       </c>
       <c r="CR19" t="s">
+        <v>131</v>
+      </c>
+      <c r="CS19" t="s">
         <v>130</v>
       </c>
-      <c r="CS19" t="s">
-        <v>129</v>
-      </c>
       <c r="CT19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -6451,292 +6454,292 @@
         <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N20" t="s">
         <v>126</v>
       </c>
       <c r="O20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q20" t="s">
         <v>126</v>
       </c>
       <c r="R20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA20" t="s">
         <v>126</v>
       </c>
       <c r="AB20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF20" t="s">
         <v>126</v>
       </c>
       <c r="AG20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI20" t="s">
         <v>126</v>
       </c>
       <c r="AJ20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG20" t="s">
         <v>126</v>
       </c>
       <c r="BH20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX20" t="s">
         <v>126</v>
       </c>
       <c r="BY20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA20" t="s">
+        <v>129</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CC20" t="s">
         <v>128</v>
       </c>
-      <c r="CB20" t="s">
-        <v>126</v>
-      </c>
-      <c r="CC20" t="s">
-        <v>127</v>
-      </c>
       <c r="CD20" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE20" t="s">
         <v>128</v>
       </c>
-      <c r="CE20" t="s">
-        <v>127</v>
-      </c>
       <c r="CF20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK20" t="s">
+        <v>129</v>
+      </c>
+      <c r="CL20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM20" t="s">
         <v>128</v>
       </c>
-      <c r="CL20" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM20" t="s">
-        <v>127</v>
-      </c>
       <c r="CN20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO20" t="s">
         <v>126</v>
       </c>
       <c r="CP20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CQ20" t="s">
         <v>126</v>
       </c>
       <c r="CR20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CS20" t="s">
         <v>134</v>
       </c>
-      <c r="CS20" t="s">
-        <v>133</v>
-      </c>
       <c r="CT20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:98">
@@ -6930,10 +6933,10 @@
         <v>126</v>
       </c>
       <c r="BL21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN21" t="s">
         <v>126</v>
@@ -6948,55 +6951,55 @@
         <v>126</v>
       </c>
       <c r="BR21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU21" t="s">
         <v>126</v>
       </c>
       <c r="BV21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC21" t="s">
         <v>126</v>
       </c>
       <c r="CD21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CH21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI21" t="s">
         <v>126</v>
@@ -7011,10 +7014,10 @@
         <v>126</v>
       </c>
       <c r="CM21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO21" t="s">
         <v>126</v>
@@ -7026,13 +7029,13 @@
         <v>126</v>
       </c>
       <c r="CR21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -7109,19 +7112,19 @@
         <v>126</v>
       </c>
       <c r="Y22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB22" t="s">
         <v>126</v>
       </c>
       <c r="AC22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD22" t="s">
         <v>126</v>
@@ -7142,7 +7145,7 @@
         <v>126</v>
       </c>
       <c r="AJ22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK22" t="s">
         <v>126</v>
@@ -7178,13 +7181,13 @@
         <v>126</v>
       </c>
       <c r="AV22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY22" t="s">
         <v>126</v>
@@ -7196,124 +7199,124 @@
         <v>126</v>
       </c>
       <c r="BB22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG22" t="s">
         <v>126</v>
       </c>
       <c r="BH22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB22" t="s">
         <v>126</v>
       </c>
       <c r="CC22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD22" t="s">
         <v>126</v>
       </c>
       <c r="CE22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG22" t="s">
         <v>126</v>
       </c>
       <c r="CH22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CP22" t="s">
         <v>126</v>
@@ -7322,13 +7325,13 @@
         <v>126</v>
       </c>
       <c r="CR22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -7339,7 +7342,7 @@
         <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>126</v>
@@ -7357,19 +7360,19 @@
         <v>126</v>
       </c>
       <c r="I23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N23" t="s">
         <v>126</v>
@@ -7378,10 +7381,10 @@
         <v>126</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R23" t="s">
         <v>126</v>
@@ -7396,235 +7399,235 @@
         <v>126</v>
       </c>
       <c r="V23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE23" t="s">
         <v>126</v>
       </c>
       <c r="AF23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS23" t="s">
         <v>126</v>
       </c>
       <c r="AT23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD23" t="s">
         <v>126</v>
       </c>
       <c r="BE23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY23" t="s">
         <v>126</v>
       </c>
       <c r="BZ23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CL23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM23" t="s">
+        <v>129</v>
+      </c>
+      <c r="CN23" t="s">
+        <v>129</v>
+      </c>
+      <c r="CO23" t="s">
+        <v>129</v>
+      </c>
+      <c r="CP23" t="s">
         <v>128</v>
       </c>
-      <c r="CN23" t="s">
+      <c r="CQ23" t="s">
         <v>128</v>
       </c>
-      <c r="CO23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ23" t="s">
-        <v>127</v>
-      </c>
       <c r="CR23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="CS23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CT23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -7635,7 +7638,7 @@
         <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
         <v>126</v>
@@ -7644,22 +7647,22 @@
         <v>126</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
         <v>126</v>
@@ -7686,10 +7689,10 @@
         <v>126</v>
       </c>
       <c r="T24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V24" t="s">
         <v>126</v>
@@ -7713,13 +7716,13 @@
         <v>126</v>
       </c>
       <c r="AC24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD24" t="s">
         <v>126</v>
       </c>
       <c r="AE24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF24" t="s">
         <v>126</v>
@@ -7728,7 +7731,7 @@
         <v>126</v>
       </c>
       <c r="AH24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI24" t="s">
         <v>126</v>
@@ -7740,61 +7743,61 @@
         <v>126</v>
       </c>
       <c r="AL24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM24" t="s">
         <v>126</v>
       </c>
       <c r="AN24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS24" t="s">
         <v>126</v>
       </c>
       <c r="AT24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC24" t="s">
         <v>126</v>
       </c>
       <c r="BD24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE24" t="s">
         <v>126</v>
@@ -7803,13 +7806,13 @@
         <v>126</v>
       </c>
       <c r="BG24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH24" t="s">
         <v>126</v>
       </c>
       <c r="BI24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ24" t="s">
         <v>126</v>
@@ -7821,106 +7824,106 @@
         <v>126</v>
       </c>
       <c r="BM24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP24" t="s">
         <v>126</v>
       </c>
       <c r="BQ24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU24" t="s">
         <v>126</v>
       </c>
       <c r="BV24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE24" t="s">
         <v>126</v>
       </c>
       <c r="CF24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG24" t="s">
         <v>126</v>
       </c>
       <c r="CH24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM24" t="s">
         <v>126</v>
       </c>
       <c r="CN24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO24" t="s">
         <v>126</v>
       </c>
       <c r="CP24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CQ24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CR24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -8141,46 +8144,46 @@
         <v>126</v>
       </c>
       <c r="BU25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV25" t="s">
         <v>126</v>
       </c>
       <c r="BW25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC25" t="s">
         <v>126</v>
       </c>
       <c r="CD25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE25" t="s">
         <v>126</v>
       </c>
       <c r="CF25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG25" t="s">
         <v>126</v>
       </c>
       <c r="CH25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI25" t="s">
         <v>126</v>
@@ -8210,13 +8213,13 @@
         <v>126</v>
       </c>
       <c r="CR25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -8224,13 +8227,13 @@
         <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
         <v>126</v>
@@ -8395,13 +8398,13 @@
         <v>126</v>
       </c>
       <c r="BG26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ26" t="s">
         <v>126</v>
@@ -8410,25 +8413,25 @@
         <v>126</v>
       </c>
       <c r="BL26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM26" t="s">
         <v>126</v>
       </c>
       <c r="BN26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP26" t="s">
         <v>126</v>
       </c>
       <c r="BQ26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS26" t="s">
         <v>126</v>
@@ -8476,7 +8479,7 @@
         <v>126</v>
       </c>
       <c r="CH26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI26" t="s">
         <v>126</v>
@@ -8506,13 +8509,13 @@
         <v>126</v>
       </c>
       <c r="CR26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CT26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -8520,7 +8523,7 @@
         <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
         <v>126</v>
@@ -8667,58 +8670,58 @@
         <v>126</v>
       </c>
       <c r="AY27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE27" t="s">
         <v>126</v>
       </c>
       <c r="BF27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI27" t="s">
         <v>126</v>
       </c>
       <c r="BJ27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK27" t="s">
         <v>126</v>
       </c>
       <c r="BL27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BO27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ27" t="s">
         <v>126</v>
@@ -8733,67 +8736,67 @@
         <v>126</v>
       </c>
       <c r="BU27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX27" t="s">
         <v>126</v>
       </c>
       <c r="BY27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA27" t="s">
         <v>126</v>
       </c>
       <c r="CB27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC27" t="s">
         <v>126</v>
       </c>
       <c r="CD27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE27" t="s">
         <v>126</v>
       </c>
       <c r="CF27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CG27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CH27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK27" t="s">
         <v>126</v>
       </c>
       <c r="CL27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM27" t="s">
         <v>126</v>
       </c>
       <c r="CN27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CO27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CP27" t="s">
         <v>126</v>
@@ -8802,13 +8805,13 @@
         <v>126</v>
       </c>
       <c r="CR27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CS27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -8816,19 +8819,19 @@
         <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
         <v>126</v>
       </c>
       <c r="F28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G28" t="s">
         <v>126</v>
@@ -8870,10 +8873,10 @@
         <v>126</v>
       </c>
       <c r="T28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V28" t="s">
         <v>126</v>
@@ -8885,91 +8888,91 @@
         <v>126</v>
       </c>
       <c r="Y28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH28" t="s">
         <v>126</v>
       </c>
       <c r="AI28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ28" t="s">
         <v>126</v>
       </c>
       <c r="AK28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN28" t="s">
         <v>126</v>
       </c>
       <c r="AO28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP28" t="s">
         <v>126</v>
       </c>
       <c r="AQ28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS28" t="s">
         <v>126</v>
       </c>
       <c r="AT28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB28" t="s">
         <v>126</v>
@@ -8978,109 +8981,109 @@
         <v>126</v>
       </c>
       <c r="BD28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE28" t="s">
         <v>126</v>
       </c>
       <c r="BF28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG28" t="s">
         <v>126</v>
       </c>
       <c r="BH28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN28" t="s">
         <v>126</v>
       </c>
       <c r="BO28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BS28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CA28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CB28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CC28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CD28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CE28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CG28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CL28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CM28" t="s">
         <v>126</v>
@@ -9098,13 +9101,13 @@
         <v>126</v>
       </c>
       <c r="CR28" t="s">
+        <v>131</v>
+      </c>
+      <c r="CS28" t="s">
         <v>130</v>
       </c>
-      <c r="CS28" t="s">
-        <v>129</v>
-      </c>
       <c r="CT28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -9112,10 +9115,10 @@
         <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>126</v>
@@ -9148,229 +9151,229 @@
         <v>126</v>
       </c>
       <c r="N29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG29" t="s">
         <v>126</v>
       </c>
       <c r="AH29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI29" t="s">
         <v>126</v>
       </c>
       <c r="AJ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM29" t="s">
         <v>126</v>
       </c>
       <c r="AN29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AS29" t="s">
         <v>126</v>
       </c>
       <c r="AT29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AU29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AW29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AY29" t="s">
         <v>126</v>
       </c>
       <c r="AZ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BA29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BB29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BC29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BF29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BG29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BI29" t="s">
         <v>126</v>
       </c>
       <c r="BJ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BN29" t="s">
         <v>126</v>
       </c>
       <c r="BO29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BP29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BQ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BR29" t="s">
         <v>126</v>
       </c>
       <c r="BS29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BT29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BU29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV29" t="s">
         <v>126</v>
       </c>
       <c r="BW29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BX29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BY29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BZ29" t="s">
+        <v>129</v>
+      </c>
+      <c r="CA29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CC29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CD29" t="s">
         <v>128</v>
       </c>
-      <c r="CA29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CC29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CD29" t="s">
-        <v>127</v>
-      </c>
       <c r="CE29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CF29" t="s">
         <v>126</v>
       </c>
       <c r="CG29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CJ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CK29" t="s">
         <v>126</v>
@@ -9379,28 +9382,28 @@
         <v>126</v>
       </c>
       <c r="CM29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CN29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CO29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CP29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CQ29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CR29" t="s">
+        <v>134</v>
+      </c>
+      <c r="CS29" t="s">
         <v>133</v>
       </c>
-      <c r="CS29" t="s">
-        <v>132</v>
-      </c>
       <c r="CT29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Fuel_(diesel,_parallel_market)_tukey_classification_matrix.xlsx
+++ b/outputs/Fuel_(diesel,_parallel_market)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="129">
   <si>
     <t>2018 Mar</t>
   </si>
@@ -400,46 +400,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>11%</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1162,7 @@
         <v>127</v>
       </c>
       <c r="AB2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AC2" t="s">
         <v>127</v>
@@ -1405,13 +1366,13 @@
         <v>126</v>
       </c>
       <c r="CR2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:98">
@@ -1551,7 +1512,7 @@
         <v>127</v>
       </c>
       <c r="AT3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AU3" t="s">
         <v>126</v>
@@ -1656,58 +1617,58 @@
         <v>127</v>
       </c>
       <c r="CC3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR3" t="s">
         <v>128</v>
       </c>
-      <c r="CD3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>129</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>131</v>
-      </c>
       <c r="CS3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CT3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:98">
@@ -1940,70 +1901,70 @@
         <v>127</v>
       </c>
       <c r="BY4" t="s">
+        <v>127</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR4" t="s">
         <v>128</v>
       </c>
-      <c r="BZ4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CA4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC4" t="s">
+      <c r="CS4" t="s">
         <v>128</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CT4" t="s">
         <v>128</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>126</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>126</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>129</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>128</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:98">
@@ -2293,13 +2254,13 @@
         <v>126</v>
       </c>
       <c r="CR5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:98">
@@ -2547,7 +2508,7 @@
         <v>126</v>
       </c>
       <c r="CD6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CE6" t="s">
         <v>127</v>
@@ -2589,13 +2550,13 @@
         <v>126</v>
       </c>
       <c r="CR6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:98">
@@ -2777,7 +2738,7 @@
         <v>126</v>
       </c>
       <c r="BH7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BI7" t="s">
         <v>126</v>
@@ -2828,10 +2789,10 @@
         <v>126</v>
       </c>
       <c r="BY7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BZ7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CA7" t="s">
         <v>126</v>
@@ -2870,7 +2831,7 @@
         <v>126</v>
       </c>
       <c r="CM7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CN7" t="s">
         <v>126</v>
@@ -2885,13 +2846,13 @@
         <v>126</v>
       </c>
       <c r="CR7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -3031,7 +2992,7 @@
         <v>127</v>
       </c>
       <c r="AT8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AU8" t="s">
         <v>126</v>
@@ -3070,7 +3031,7 @@
         <v>126</v>
       </c>
       <c r="BG8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BH8" t="s">
         <v>127</v>
@@ -3181,13 +3142,13 @@
         <v>126</v>
       </c>
       <c r="CR8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -3477,13 +3438,13 @@
         <v>126</v>
       </c>
       <c r="CR9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -3491,10 +3452,10 @@
         <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s">
         <v>126</v>
@@ -3662,7 +3623,7 @@
         <v>126</v>
       </c>
       <c r="BG10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BH10" t="s">
         <v>126</v>
@@ -3680,7 +3641,7 @@
         <v>126</v>
       </c>
       <c r="BM10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BN10" t="s">
         <v>127</v>
@@ -3713,7 +3674,7 @@
         <v>126</v>
       </c>
       <c r="BX10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BY10" t="s">
         <v>126</v>
@@ -3773,13 +3734,13 @@
         <v>126</v>
       </c>
       <c r="CR10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -4039,19 +4000,19 @@
         <v>126</v>
       </c>
       <c r="CH11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CI11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CJ11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CK11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CL11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CM11" t="s">
         <v>126</v>
@@ -4069,13 +4030,13 @@
         <v>126</v>
       </c>
       <c r="CR11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -4257,7 +4218,7 @@
         <v>126</v>
       </c>
       <c r="BH12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BI12" t="s">
         <v>126</v>
@@ -4266,7 +4227,7 @@
         <v>126</v>
       </c>
       <c r="BK12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BL12" t="s">
         <v>127</v>
@@ -4326,16 +4287,16 @@
         <v>126</v>
       </c>
       <c r="CE12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CF12" t="s">
         <v>126</v>
       </c>
       <c r="CG12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CH12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CI12" t="s">
         <v>126</v>
@@ -4365,13 +4326,13 @@
         <v>126</v>
       </c>
       <c r="CR12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -4556,10 +4517,10 @@
         <v>127</v>
       </c>
       <c r="BI13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BJ13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BK13" t="s">
         <v>127</v>
@@ -4649,25 +4610,25 @@
         <v>127</v>
       </c>
       <c r="CN13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CO13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CP13" t="s">
         <v>127</v>
       </c>
       <c r="CQ13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CR13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -4924,46 +4885,46 @@
         <v>127</v>
       </c>
       <c r="CG14" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH14" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI14" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CK14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CL14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CN14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CO14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR14" t="s">
         <v>128</v>
       </c>
-      <c r="CH14" t="s">
+      <c r="CS14" t="s">
         <v>128</v>
       </c>
-      <c r="CI14" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CK14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CL14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CN14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR14" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS14" t="s">
-        <v>130</v>
-      </c>
       <c r="CT14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -4974,7 +4935,7 @@
         <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
         <v>126</v>
@@ -5187,13 +5148,13 @@
         <v>126</v>
       </c>
       <c r="BV15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BW15" t="s">
         <v>127</v>
       </c>
       <c r="BX15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BY15" t="s">
         <v>127</v>
@@ -5208,7 +5169,7 @@
         <v>127</v>
       </c>
       <c r="CC15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CD15" t="s">
         <v>126</v>
@@ -5253,13 +5214,13 @@
         <v>127</v>
       </c>
       <c r="CR15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -5354,7 +5315,7 @@
         <v>127</v>
       </c>
       <c r="AE16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF16" t="s">
         <v>127</v>
@@ -5402,7 +5363,7 @@
         <v>127</v>
       </c>
       <c r="AU16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AV16" t="s">
         <v>126</v>
@@ -5441,10 +5402,10 @@
         <v>126</v>
       </c>
       <c r="BH16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BI16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BJ16" t="s">
         <v>127</v>
@@ -5456,7 +5417,7 @@
         <v>126</v>
       </c>
       <c r="BM16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BN16" t="s">
         <v>127</v>
@@ -5489,7 +5450,7 @@
         <v>127</v>
       </c>
       <c r="BX16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BY16" t="s">
         <v>126</v>
@@ -5504,7 +5465,7 @@
         <v>126</v>
       </c>
       <c r="CC16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CD16" t="s">
         <v>127</v>
@@ -5549,13 +5510,13 @@
         <v>126</v>
       </c>
       <c r="CR16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -5788,7 +5749,7 @@
         <v>126</v>
       </c>
       <c r="BY17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BZ17" t="s">
         <v>127</v>
@@ -5797,7 +5758,7 @@
         <v>127</v>
       </c>
       <c r="CB17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="CC17" t="s">
         <v>127</v>
@@ -5809,49 +5770,49 @@
         <v>127</v>
       </c>
       <c r="CF17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="CG17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI17" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN17" t="s">
+        <v>126</v>
+      </c>
+      <c r="CO17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP17" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ17" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR17" t="s">
         <v>128</v>
       </c>
-      <c r="CH17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CJ17" t="s">
+      <c r="CS17" t="s">
         <v>128</v>
       </c>
-      <c r="CK17" t="s">
+      <c r="CT17" t="s">
         <v>128</v>
-      </c>
-      <c r="CL17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR17" t="s">
-        <v>134</v>
-      </c>
-      <c r="CS17" t="s">
-        <v>134</v>
-      </c>
-      <c r="CT17" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -6102,52 +6063,52 @@
         <v>127</v>
       </c>
       <c r="CE18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CO18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ18" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR18" t="s">
         <v>128</v>
       </c>
-      <c r="CF18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CG18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CJ18" t="s">
+      <c r="CS18" t="s">
         <v>128</v>
       </c>
-      <c r="CK18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP18" t="s">
+      <c r="CT18" t="s">
         <v>128</v>
-      </c>
-      <c r="CQ18" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR18" t="s">
-        <v>134</v>
-      </c>
-      <c r="CS18" t="s">
-        <v>133</v>
-      </c>
-      <c r="CT18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -6254,7 +6215,7 @@
         <v>127</v>
       </c>
       <c r="AI19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AJ19" t="s">
         <v>126</v>
@@ -6266,7 +6227,7 @@
         <v>127</v>
       </c>
       <c r="AM19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AN19" t="s">
         <v>127</v>
@@ -6296,7 +6257,7 @@
         <v>127</v>
       </c>
       <c r="AW19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AX19" t="s">
         <v>127</v>
@@ -6383,67 +6344,67 @@
         <v>126</v>
       </c>
       <c r="BZ19" t="s">
+        <v>127</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CC19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CE19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CF19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CH19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CK19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CL19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ19" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR19" t="s">
         <v>128</v>
       </c>
-      <c r="CA19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CD19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CE19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CF19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CG19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CH19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CI19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CJ19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CK19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CL19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CN19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ19" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR19" t="s">
-        <v>131</v>
-      </c>
       <c r="CS19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -6682,64 +6643,64 @@
         <v>127</v>
       </c>
       <c r="CA20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="CB20" t="s">
         <v>127</v>
       </c>
       <c r="CC20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO20" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP20" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ20" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR20" t="s">
         <v>128</v>
       </c>
-      <c r="CD20" t="s">
-        <v>129</v>
-      </c>
-      <c r="CE20" t="s">
+      <c r="CS20" t="s">
         <v>128</v>
       </c>
-      <c r="CF20" t="s">
+      <c r="CT20" t="s">
         <v>128</v>
-      </c>
-      <c r="CG20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH20" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CJ20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CK20" t="s">
-        <v>129</v>
-      </c>
-      <c r="CL20" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN20" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO20" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ20" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CS20" t="s">
-        <v>134</v>
-      </c>
-      <c r="CT20" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:98">
@@ -6966,7 +6927,7 @@
         <v>127</v>
       </c>
       <c r="BW21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BX21" t="s">
         <v>127</v>
@@ -6975,7 +6936,7 @@
         <v>127</v>
       </c>
       <c r="BZ21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CA21" t="s">
         <v>127</v>
@@ -6996,7 +6957,7 @@
         <v>127</v>
       </c>
       <c r="CG21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CH21" t="s">
         <v>127</v>
@@ -7029,13 +6990,13 @@
         <v>126</v>
       </c>
       <c r="CR21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -7325,13 +7286,13 @@
         <v>126</v>
       </c>
       <c r="CR22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -7585,49 +7546,49 @@
         <v>127</v>
       </c>
       <c r="CF23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR23" t="s">
         <v>128</v>
       </c>
-      <c r="CG23" t="s">
+      <c r="CS23" t="s">
         <v>128</v>
       </c>
-      <c r="CH23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI23" t="s">
+      <c r="CT23" t="s">
         <v>128</v>
-      </c>
-      <c r="CJ23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CK23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CL23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM23" t="s">
-        <v>129</v>
-      </c>
-      <c r="CN23" t="s">
-        <v>129</v>
-      </c>
-      <c r="CO23" t="s">
-        <v>129</v>
-      </c>
-      <c r="CP23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CR23" t="s">
-        <v>136</v>
-      </c>
-      <c r="CS23" t="s">
-        <v>134</v>
-      </c>
-      <c r="CT23" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -7917,13 +7878,13 @@
         <v>127</v>
       </c>
       <c r="CR24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -8144,46 +8105,46 @@
         <v>126</v>
       </c>
       <c r="BU25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BV25" t="s">
         <v>126</v>
       </c>
       <c r="BW25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BX25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BY25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BZ25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CA25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CB25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CC25" t="s">
         <v>126</v>
       </c>
       <c r="CD25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CE25" t="s">
         <v>126</v>
       </c>
       <c r="CF25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CG25" t="s">
         <v>126</v>
       </c>
       <c r="CH25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CI25" t="s">
         <v>126</v>
@@ -8213,13 +8174,13 @@
         <v>126</v>
       </c>
       <c r="CR25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -8233,7 +8194,7 @@
         <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
         <v>126</v>
@@ -8398,7 +8359,7 @@
         <v>126</v>
       </c>
       <c r="BG26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BH26" t="s">
         <v>127</v>
@@ -8413,25 +8374,25 @@
         <v>126</v>
       </c>
       <c r="BL26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BM26" t="s">
         <v>126</v>
       </c>
       <c r="BN26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BO26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BP26" t="s">
         <v>126</v>
       </c>
       <c r="BQ26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BR26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BS26" t="s">
         <v>126</v>
@@ -8479,7 +8440,7 @@
         <v>126</v>
       </c>
       <c r="CH26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CI26" t="s">
         <v>126</v>
@@ -8509,13 +8470,13 @@
         <v>126</v>
       </c>
       <c r="CR26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -8694,7 +8655,7 @@
         <v>127</v>
       </c>
       <c r="BG27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BH27" t="s">
         <v>127</v>
@@ -8769,7 +8730,7 @@
         <v>126</v>
       </c>
       <c r="CF27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="CG27" t="s">
         <v>127</v>
@@ -8796,7 +8757,7 @@
         <v>127</v>
       </c>
       <c r="CO27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="CP27" t="s">
         <v>126</v>
@@ -8805,13 +8766,13 @@
         <v>126</v>
       </c>
       <c r="CR27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CS27" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="CT27" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -9068,46 +9029,46 @@
         <v>127</v>
       </c>
       <c r="CG28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM28" t="s">
+        <v>126</v>
+      </c>
+      <c r="CN28" t="s">
+        <v>126</v>
+      </c>
+      <c r="CO28" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP28" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ28" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR28" t="s">
         <v>128</v>
       </c>
-      <c r="CH28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM28" t="s">
-        <v>126</v>
-      </c>
-      <c r="CN28" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO28" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP28" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ28" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR28" t="s">
-        <v>131</v>
-      </c>
       <c r="CS28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CT28" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -9343,7 +9304,7 @@
         <v>127</v>
       </c>
       <c r="BZ29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="CA29" t="s">
         <v>127</v>
@@ -9355,55 +9316,55 @@
         <v>126</v>
       </c>
       <c r="CD29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CG29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CL29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR29" t="s">
         <v>128</v>
       </c>
-      <c r="CE29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CG29" t="s">
+      <c r="CS29" t="s">
         <v>128</v>
       </c>
-      <c r="CH29" t="s">
+      <c r="CT29" t="s">
         <v>128</v>
-      </c>
-      <c r="CI29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CL29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN29" t="s">
-        <v>129</v>
-      </c>
-      <c r="CO29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR29" t="s">
-        <v>134</v>
-      </c>
-      <c r="CS29" t="s">
-        <v>133</v>
-      </c>
-      <c r="CT29" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Fuel_(diesel,_parallel_market)_tukey_classification_matrix.xlsx
+++ b/outputs/Fuel_(diesel,_parallel_market)_tukey_classification_matrix.xlsx
@@ -397,7 +397,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
